--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136171071</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136171071</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136171071</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136171071</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57530-2023 artfynd.xlsx
+++ b/artfynd/A 57530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136171172</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136171433</v>
       </c>
       <c r="B4" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
